--- a/artfynd/Juånäset artfynd.xlsx
+++ b/artfynd/Juånäset artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110875612</v>
+        <v>110875587</v>
       </c>
       <c r="B2" t="n">
-        <v>97358</v>
+        <v>80298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520646</v>
+        <v>520528</v>
       </c>
       <c r="R2" t="n">
-        <v>6920103</v>
+        <v>6919888</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,6 +754,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,32 +778,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110875604</v>
+        <v>110875588</v>
       </c>
       <c r="B3" t="n">
-        <v>79359</v>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520248</v>
+        <v>520530</v>
       </c>
       <c r="R3" t="n">
-        <v>6920087</v>
+        <v>6919898</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -856,17 +857,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -884,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110875605</v>
+        <v>110875583</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +892,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520254</v>
+        <v>520663</v>
       </c>
       <c r="R4" t="n">
-        <v>6920081</v>
+        <v>6919878</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -973,7 +970,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -991,51 +988,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110875606</v>
+        <v>119009764</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>57258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>100065</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520371</v>
+        <v>520597</v>
       </c>
       <c r="R5" t="n">
-        <v>6920053</v>
+        <v>6919810</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1059,12 +1057,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,39 +1081,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110875609</v>
+        <v>119009897</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>58541</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,34 +1110,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>102987</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520529</v>
+        <v>520351</v>
       </c>
       <c r="R6" t="n">
-        <v>6920018</v>
+        <v>6919899</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1167,12 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,71 +1194,65 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110875587</v>
+        <v>110875585</v>
       </c>
       <c r="B7" t="n">
-        <v>80298</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>388</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520528</v>
+        <v>520663</v>
       </c>
       <c r="R7" t="n">
-        <v>6919888</v>
+        <v>6919878</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1288,7 +1293,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1312,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110875594</v>
+        <v>110875612</v>
       </c>
       <c r="B8" t="n">
-        <v>92208</v>
+        <v>97358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520387</v>
+        <v>520646</v>
       </c>
       <c r="R8" t="n">
-        <v>6919941</v>
+        <v>6920103</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1414,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110875598</v>
+        <v>110875604</v>
       </c>
       <c r="B9" t="n">
-        <v>92208</v>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1425,21 +1429,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520214</v>
+        <v>520248</v>
       </c>
       <c r="R9" t="n">
-        <v>6919983</v>
+        <v>6920087</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1499,6 +1503,11 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>Barrnaturskog lövrik barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1516,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110875593</v>
+        <v>110875605</v>
       </c>
       <c r="B10" t="n">
-        <v>91909</v>
+        <v>79359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1536,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520404</v>
+        <v>520254</v>
       </c>
       <c r="R10" t="n">
-        <v>6919950</v>
+        <v>6920081</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1601,6 +1610,11 @@
       <c r="AI10" t="inlineStr">
         <is>
           <t>Barrnaturskog lövrik barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1618,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110875595</v>
+        <v>110875606</v>
       </c>
       <c r="B11" t="n">
-        <v>92369</v>
+        <v>79359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,34 +1643,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520387</v>
+        <v>520371</v>
       </c>
       <c r="R11" t="n">
-        <v>6919941</v>
+        <v>6920053</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1697,12 +1714,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
           <t>Barrnaturskog lövrik barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1720,32 +1743,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110875588</v>
+        <v>110875609</v>
       </c>
       <c r="B12" t="n">
-        <v>96601</v>
+        <v>79359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2170</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520530</v>
+        <v>520529</v>
       </c>
       <c r="R12" t="n">
-        <v>6919898</v>
+        <v>6920018</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1799,13 +1822,17 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
           <t>Barrnaturskog lövrik barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1823,32 +1850,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110875591</v>
+        <v>110875594</v>
       </c>
       <c r="B13" t="n">
-        <v>96601</v>
+        <v>92208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2170</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1858,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520514</v>
+        <v>520387</v>
       </c>
       <c r="R13" t="n">
-        <v>6919926</v>
+        <v>6919941</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1925,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110875597</v>
+        <v>110875598</v>
       </c>
       <c r="B14" t="n">
-        <v>93197</v>
+        <v>92208</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1960,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520275</v>
+        <v>520214</v>
       </c>
       <c r="R14" t="n">
-        <v>6919992</v>
+        <v>6919983</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2027,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110875583</v>
+        <v>110875593</v>
       </c>
       <c r="B15" t="n">
-        <v>79084</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,21 +2065,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2062,10 +2089,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520663</v>
+        <v>520404</v>
       </c>
       <c r="R15" t="n">
-        <v>6919878</v>
+        <v>6919950</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2112,11 +2139,6 @@
       <c r="AI15" t="inlineStr">
         <is>
           <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2134,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110875589</v>
+        <v>110875595</v>
       </c>
       <c r="B16" t="n">
-        <v>79946</v>
+        <v>92369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2145,21 +2167,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2169,10 +2191,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520514</v>
+        <v>520387</v>
       </c>
       <c r="R16" t="n">
-        <v>6919926</v>
+        <v>6919941</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2219,11 +2241,6 @@
       <c r="AI16" t="inlineStr">
         <is>
           <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2241,10 +2258,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110875610</v>
+        <v>110875591</v>
       </c>
       <c r="B17" t="n">
-        <v>80336</v>
+        <v>96601</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,21 +2269,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>2170</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2276,10 +2293,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520617</v>
+        <v>520514</v>
       </c>
       <c r="R17" t="n">
-        <v>6920082</v>
+        <v>6919926</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2343,52 +2360,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119009764</v>
+        <v>110875597</v>
       </c>
       <c r="B18" t="n">
-        <v>57258</v>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100065</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520597</v>
+        <v>520275</v>
       </c>
       <c r="R18" t="n">
-        <v>6919810</v>
+        <v>6919992</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2412,22 +2425,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2438,26 +2441,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Barrnaturskog lövrik barrblandskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119009897</v>
+        <v>110875589</v>
       </c>
       <c r="B19" t="n">
-        <v>58541</v>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,38 +2473,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102987</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520351</v>
+        <v>520514</v>
       </c>
       <c r="R19" t="n">
-        <v>6919899</v>
+        <v>6919926</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2523,22 +2527,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>05:30</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>05:30</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2549,26 +2543,36 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Barrnaturskog lövrik barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119009829</v>
+        <v>110875610</v>
       </c>
       <c r="B20" t="n">
-        <v>58327</v>
+        <v>80336</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2576,41 +2580,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520110</v>
+        <v>520617</v>
       </c>
       <c r="R20" t="n">
-        <v>6920067</v>
+        <v>6920082</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2634,22 +2634,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>04:51</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>04:51</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2660,23 +2650,28 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Barrnaturskog lövrik barrblandskog</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119009830</v>
+        <v>119009829</v>
       </c>
       <c r="B21" t="n">
         <v>58327</v>
@@ -2715,13 +2710,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520217</v>
+        <v>520110</v>
       </c>
       <c r="R21" t="n">
-        <v>6920115</v>
+        <v>6920067</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2750,7 +2745,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>04:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2760,7 +2755,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>04:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2787,7 +2782,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119009887</v>
+        <v>119009830</v>
       </c>
       <c r="B22" t="n">
         <v>58327</v>
@@ -2826,10 +2821,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520690</v>
+        <v>520217</v>
       </c>
       <c r="R22" t="n">
-        <v>6920086</v>
+        <v>6920115</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2861,7 +2856,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2871,7 +2866,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2898,10 +2893,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119010377</v>
+        <v>119009887</v>
       </c>
       <c r="B23" t="n">
-        <v>58439</v>
+        <v>58327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2909,21 +2904,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2937,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520619</v>
+        <v>520690</v>
       </c>
       <c r="R23" t="n">
-        <v>6919945</v>
+        <v>6920086</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2967,22 +2962,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>05:36</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>05:36</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3009,10 +3004,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>110875602</v>
+        <v>119010377</v>
       </c>
       <c r="B24" t="n">
-        <v>99022</v>
+        <v>58439</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3020,26 +3015,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220093</v>
+        <v>103018</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3048,10 +3043,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520177</v>
+        <v>520619</v>
       </c>
       <c r="R24" t="n">
-        <v>6920007</v>
+        <v>6919945</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3078,12 +3073,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>05:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>05:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3094,58 +3099,53 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>110875585</v>
+        <v>110875602</v>
       </c>
       <c r="B25" t="n">
-        <v>99118</v>
+        <v>99022</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520663</v>
+        <v>520177</v>
       </c>
       <c r="R25" t="n">
-        <v>6919878</v>
+        <v>6920007</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -4173,52 +4173,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119009653</v>
+        <v>110875564</v>
       </c>
       <c r="B35" t="n">
-        <v>57950</v>
+        <v>92208</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521181</v>
+        <v>520963</v>
       </c>
       <c r="R35" t="n">
-        <v>6919622</v>
+        <v>6919882</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4242,27 +4238,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>07:48</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>07:48</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4273,76 +4254,69 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Barrnaturskog lövrik barrblandskog</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119009758</v>
+        <v>110875565</v>
       </c>
       <c r="B36" t="n">
-        <v>57950</v>
+        <v>91909</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521139</v>
+        <v>520939</v>
       </c>
       <c r="R36" t="n">
-        <v>6919778</v>
+        <v>6919889</v>
       </c>
       <c r="S36" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4366,27 +4340,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>flyktläte</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4397,68 +4356,69 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Barrnaturskog lövrik barrblandskog</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119009655</v>
+        <v>110875576</v>
       </c>
       <c r="B37" t="n">
-        <v>57340</v>
+        <v>92369</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100091</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521117</v>
+        <v>520871</v>
       </c>
       <c r="R37" t="n">
-        <v>6919656</v>
+        <v>6919906</v>
       </c>
       <c r="S37" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4482,22 +4442,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>07:18</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>07:18</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4508,65 +4458,66 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Barrnaturskog lövrik barrblandskog</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119009846</v>
+        <v>110875578</v>
       </c>
       <c r="B38" t="n">
-        <v>58439</v>
+        <v>93197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103018</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521095</v>
+        <v>520770</v>
       </c>
       <c r="R38" t="n">
-        <v>6919757</v>
+        <v>6919888</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4593,22 +4544,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4619,68 +4560,69 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Barrnaturskog lövrik barrblandskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119010382</v>
+        <v>110875580</v>
       </c>
       <c r="B39" t="n">
-        <v>58085</v>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>205976</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>521054</v>
+        <v>520721</v>
       </c>
       <c r="R39" t="n">
-        <v>6919621</v>
+        <v>6919849</v>
       </c>
       <c r="S39" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4704,27 +4646,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>04:41</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>04:41</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4735,48 +4662,58 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Barrnaturskog lövrik barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>110875538</v>
+        <v>110875555</v>
       </c>
       <c r="B40" t="n">
-        <v>97358</v>
+        <v>80336</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4786,10 +4723,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>521333</v>
+        <v>521191</v>
       </c>
       <c r="R40" t="n">
-        <v>6920162</v>
+        <v>6919851</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4853,10 +4790,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>110875618</v>
+        <v>110875552</v>
       </c>
       <c r="B41" t="n">
-        <v>78993</v>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4864,21 +4801,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4888,10 +4825,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520912</v>
+        <v>521229</v>
       </c>
       <c r="R41" t="n">
-        <v>6920129</v>
+        <v>6919828</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4955,10 +4892,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>110875547</v>
+        <v>110875557</v>
       </c>
       <c r="B42" t="n">
-        <v>92208</v>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4966,21 +4903,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4990,10 +4927,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>521322</v>
+        <v>521147</v>
       </c>
       <c r="R42" t="n">
-        <v>6919915</v>
+        <v>6919871</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5057,10 +4994,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>110875564</v>
+        <v>110875559</v>
       </c>
       <c r="B43" t="n">
-        <v>92208</v>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5068,21 +5005,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5092,7 +5029,7 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520963</v>
+        <v>521098</v>
       </c>
       <c r="R43" t="n">
         <v>6919882</v>
@@ -5159,32 +5096,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>110875548</v>
+        <v>110875553</v>
       </c>
       <c r="B44" t="n">
-        <v>91909</v>
+        <v>80461</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5194,10 +5131,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>521322</v>
+        <v>521191</v>
       </c>
       <c r="R44" t="n">
-        <v>6919915</v>
+        <v>6919851</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5261,32 +5198,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>110875565</v>
+        <v>110875554</v>
       </c>
       <c r="B45" t="n">
-        <v>91909</v>
+        <v>80467</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5296,10 +5233,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520939</v>
+        <v>521191</v>
       </c>
       <c r="R45" t="n">
-        <v>6919889</v>
+        <v>6919851</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5363,48 +5300,52 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>110875576</v>
+        <v>119009653</v>
       </c>
       <c r="B46" t="n">
-        <v>92369</v>
+        <v>57950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520871</v>
+        <v>521181</v>
       </c>
       <c r="R46" t="n">
-        <v>6919906</v>
+        <v>6919622</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5428,12 +5369,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>07:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5444,69 +5400,76 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>110875549</v>
+        <v>119009758</v>
       </c>
       <c r="B47" t="n">
-        <v>93197</v>
+        <v>57950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>521322</v>
+        <v>521139</v>
       </c>
       <c r="R47" t="n">
-        <v>6919915</v>
+        <v>6919778</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5530,12 +5493,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>flyktläte</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5546,69 +5524,68 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>110875578</v>
+        <v>119009655</v>
       </c>
       <c r="B48" t="n">
-        <v>93197</v>
+        <v>57340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>100091</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>520770</v>
+        <v>521117</v>
       </c>
       <c r="R48" t="n">
-        <v>6919888</v>
+        <v>6919656</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5632,12 +5609,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5648,66 +5635,65 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>110875617</v>
+        <v>119009846</v>
       </c>
       <c r="B49" t="n">
-        <v>93197</v>
+        <v>58439</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>103018</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>520912</v>
+        <v>521095</v>
       </c>
       <c r="R49" t="n">
-        <v>6920129</v>
+        <v>6919757</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5734,12 +5720,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5750,69 +5746,68 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>110875574</v>
+        <v>119010382</v>
       </c>
       <c r="B50" t="n">
-        <v>79327</v>
+        <v>58085</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>205976</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520910</v>
+        <v>521054</v>
       </c>
       <c r="R50" t="n">
-        <v>6919921</v>
+        <v>6919621</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5836,12 +5831,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>04:41</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>04:41</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5852,66 +5862,65 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>110875580</v>
+        <v>110875551</v>
       </c>
       <c r="B51" t="n">
-        <v>79084</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520721</v>
+        <v>521266</v>
       </c>
       <c r="R51" t="n">
-        <v>6919849</v>
+        <v>6919806</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5958,11 +5967,6 @@
       <c r="AI51" t="inlineStr">
         <is>
           <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5980,32 +5984,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>110875555</v>
+        <v>110875558</v>
       </c>
       <c r="B52" t="n">
-        <v>80336</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6015,10 +6019,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>521191</v>
+        <v>521114</v>
       </c>
       <c r="R52" t="n">
-        <v>6919851</v>
+        <v>6919879</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6082,45 +6086,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>110875552</v>
+        <v>110875562</v>
       </c>
       <c r="B53" t="n">
-        <v>80432</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>521229</v>
+        <v>521036</v>
       </c>
       <c r="R53" t="n">
-        <v>6919828</v>
+        <v>6919871</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6184,45 +6192,49 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>110875557</v>
+        <v>110875563</v>
       </c>
       <c r="B54" t="n">
-        <v>80432</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>521147</v>
+        <v>520998</v>
       </c>
       <c r="R54" t="n">
-        <v>6919871</v>
+        <v>6919868</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6286,45 +6298,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>110875559</v>
+        <v>110875567</v>
       </c>
       <c r="B55" t="n">
-        <v>80432</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>521098</v>
+        <v>520934</v>
       </c>
       <c r="R55" t="n">
-        <v>6919882</v>
+        <v>6919896</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6388,32 +6404,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>110875553</v>
+        <v>110875577</v>
       </c>
       <c r="B56" t="n">
-        <v>80461</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6423,10 +6439,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>521191</v>
+        <v>520838</v>
       </c>
       <c r="R56" t="n">
-        <v>6919851</v>
+        <v>6919904</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6490,45 +6506,49 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>110875571</v>
+        <v>110875581</v>
       </c>
       <c r="B57" t="n">
-        <v>80461</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520920</v>
+        <v>520721</v>
       </c>
       <c r="R57" t="n">
-        <v>6919915</v>
+        <v>6919849</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6592,10 +6612,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>110875554</v>
+        <v>110875550</v>
       </c>
       <c r="B58" t="n">
-        <v>80467</v>
+        <v>106244</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6603,21 +6623,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6627,10 +6647,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>521191</v>
+        <v>521287</v>
       </c>
       <c r="R58" t="n">
-        <v>6919851</v>
+        <v>6919822</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6694,10 +6714,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>110875570</v>
+        <v>110875561</v>
       </c>
       <c r="B59" t="n">
-        <v>80467</v>
+        <v>106244</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6705,34 +6725,38 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6463</v>
+        <v>221144</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520920</v>
+        <v>521062</v>
       </c>
       <c r="R59" t="n">
-        <v>6919915</v>
+        <v>6919876</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6796,53 +6820,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>110875620</v>
+        <v>110875566</v>
       </c>
       <c r="B60" t="n">
-        <v>57953</v>
+        <v>106244</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>520929</v>
+        <v>520939</v>
       </c>
       <c r="R60" t="n">
-        <v>6920108</v>
+        <v>6919889</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6875,11 +6891,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2023-07-14</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Spår på trädstam av gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6911,52 +6922,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119009658</v>
+        <v>110875556</v>
       </c>
       <c r="B61" t="n">
-        <v>57141</v>
+        <v>79085</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>521098</v>
+        <v>521145</v>
       </c>
       <c r="R61" t="n">
-        <v>6920235</v>
+        <v>6919884</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6980,27 +6987,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>06:28</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>06:28</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>färsk</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7011,72 +7003,74 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Barrnaturskog lövrik barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119010365</v>
+        <v>110875579</v>
       </c>
       <c r="B62" t="n">
-        <v>57141</v>
+        <v>79085</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520949</v>
+        <v>520770</v>
       </c>
       <c r="R62" t="n">
-        <v>6920237</v>
+        <v>6919888</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7100,27 +7094,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>07:12</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>tupp, uppflygande</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7131,65 +7110,71 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Barrnaturskog lövrik barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119009888</v>
+        <v>110875582</v>
       </c>
       <c r="B63" t="n">
-        <v>58327</v>
+        <v>79085</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520819</v>
+        <v>520721</v>
       </c>
       <c r="R63" t="n">
-        <v>6920147</v>
+        <v>6919849</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7216,22 +7201,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>06:34</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>06:34</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7242,26 +7217,36 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Barrnaturskog lövrik barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119009765</v>
+        <v>110875538</v>
       </c>
       <c r="B64" t="n">
-        <v>58114</v>
+        <v>97358</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7269,41 +7254,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>521030</v>
+        <v>521333</v>
       </c>
       <c r="R64" t="n">
-        <v>6919924</v>
+        <v>6920162</v>
       </c>
       <c r="S64" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7327,22 +7308,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7353,68 +7324,69 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Barrnaturskog lövrik barrblandskog</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119010380</v>
+        <v>110875618</v>
       </c>
       <c r="B65" t="n">
-        <v>58636</v>
+        <v>78993</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103044</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>520994</v>
+        <v>520912</v>
       </c>
       <c r="R65" t="n">
-        <v>6920066</v>
+        <v>6920129</v>
       </c>
       <c r="S65" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7438,22 +7410,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>05:02</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>05:02</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7464,65 +7426,66 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Barrnaturskog lövrik barrblandskog</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>110875551</v>
+        <v>110875547</v>
       </c>
       <c r="B66" t="n">
-        <v>99118</v>
+        <v>92208</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>521266</v>
+        <v>521322</v>
       </c>
       <c r="R66" t="n">
-        <v>6919806</v>
+        <v>6919915</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7586,32 +7549,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>110875558</v>
+        <v>110875548</v>
       </c>
       <c r="B67" t="n">
-        <v>99118</v>
+        <v>91909</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7621,10 +7584,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>521114</v>
+        <v>521322</v>
       </c>
       <c r="R67" t="n">
-        <v>6919879</v>
+        <v>6919915</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7688,49 +7651,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>110875562</v>
+        <v>110875549</v>
       </c>
       <c r="B68" t="n">
-        <v>99118</v>
+        <v>93197</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>521036</v>
+        <v>521322</v>
       </c>
       <c r="R68" t="n">
-        <v>6919871</v>
+        <v>6919915</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7794,49 +7753,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>110875563</v>
+        <v>110875617</v>
       </c>
       <c r="B69" t="n">
-        <v>99118</v>
+        <v>93197</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520998</v>
+        <v>520912</v>
       </c>
       <c r="R69" t="n">
-        <v>6919868</v>
+        <v>6920129</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7900,10 +7855,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>110875567</v>
+        <v>110875574</v>
       </c>
       <c r="B70" t="n">
-        <v>99118</v>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7911,38 +7866,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520934</v>
+        <v>520910</v>
       </c>
       <c r="R70" t="n">
-        <v>6919896</v>
+        <v>6919921</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8006,32 +7957,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>110875577</v>
+        <v>110875629</v>
       </c>
       <c r="B71" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8041,10 +7992,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>520838</v>
+        <v>521153</v>
       </c>
       <c r="R71" t="n">
-        <v>6919904</v>
+        <v>6920292</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8108,49 +8059,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>110875581</v>
+        <v>110875571</v>
       </c>
       <c r="B72" t="n">
-        <v>99118</v>
+        <v>80461</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520721</v>
+        <v>520920</v>
       </c>
       <c r="R72" t="n">
-        <v>6919849</v>
+        <v>6919915</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8214,49 +8161,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>110875615</v>
+        <v>110875570</v>
       </c>
       <c r="B73" t="n">
-        <v>99118</v>
+        <v>80467</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>520792</v>
+        <v>520920</v>
       </c>
       <c r="R73" t="n">
-        <v>6920150</v>
+        <v>6919915</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8320,49 +8263,53 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>110875616</v>
+        <v>110875620</v>
       </c>
       <c r="B74" t="n">
-        <v>99118</v>
+        <v>57953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520853</v>
+        <v>520929</v>
       </c>
       <c r="R74" t="n">
-        <v>6920144</v>
+        <v>6920108</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8395,6 +8342,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2023-07-14</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Spår på trädstam av gran</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8426,37 +8378,37 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>110875622</v>
+        <v>119009658</v>
       </c>
       <c r="B75" t="n">
-        <v>99118</v>
+        <v>57141</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8465,13 +8417,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>520967</v>
+        <v>521098</v>
       </c>
       <c r="R75" t="n">
-        <v>6920100</v>
+        <v>6920235</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8495,12 +8447,27 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>06:28</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>06:28</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>färsk</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8511,69 +8478,72 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>110875627</v>
+        <v>119010365</v>
       </c>
       <c r="B76" t="n">
-        <v>99118</v>
+        <v>57141</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>521039</v>
+        <v>520949</v>
       </c>
       <c r="R76" t="n">
-        <v>6920135</v>
+        <v>6920237</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8597,12 +8567,27 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>tupp, uppflygande</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8613,58 +8598,53 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>110875628</v>
+        <v>119009888</v>
       </c>
       <c r="B77" t="n">
-        <v>99118</v>
+        <v>58327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8673,10 +8653,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>521023</v>
+        <v>520819</v>
       </c>
       <c r="R77" t="n">
-        <v>6920151</v>
+        <v>6920147</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8703,12 +8683,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8719,69 +8709,68 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>110875550</v>
+        <v>119009759</v>
       </c>
       <c r="B78" t="n">
-        <v>106244</v>
+        <v>58114</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>521287</v>
+        <v>521139</v>
       </c>
       <c r="R78" t="n">
-        <v>6919822</v>
+        <v>6920367</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8805,12 +8794,27 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>övr läten</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8821,58 +8825,53 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>110875561</v>
+        <v>119009765</v>
       </c>
       <c r="B79" t="n">
-        <v>106244</v>
+        <v>58114</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8881,13 +8880,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>521062</v>
+        <v>521030</v>
       </c>
       <c r="R79" t="n">
-        <v>6919876</v>
+        <v>6919924</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8911,12 +8910,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8927,31 +8936,26 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>110875566</v>
+        <v>119010380</v>
       </c>
       <c r="B80" t="n">
-        <v>106244</v>
+        <v>58636</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8959,37 +8963,41 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221144</v>
+        <v>103044</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>520939</v>
+        <v>520994</v>
       </c>
       <c r="R80" t="n">
-        <v>6919889</v>
+        <v>6920066</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9013,12 +9021,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>05:02</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>05:02</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9029,66 +9047,61 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>110875572</v>
+        <v>110860499</v>
       </c>
       <c r="B81" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Juånäset, Mpd</t>
+          <t>Juånäsberget, Mpd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>520920</v>
+        <v>521113</v>
       </c>
       <c r="R81" t="n">
-        <v>6919915</v>
+        <v>6920246</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9140,61 +9153,61 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
+          <t>Sebastian Kirppu, Karolin Hård</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>110875575</v>
+        <v>110860500</v>
       </c>
       <c r="B82" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Juånäset, Mpd</t>
+          <t>Juånäsberget, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>520911</v>
+        <v>521142</v>
       </c>
       <c r="R82" t="n">
-        <v>6919914</v>
+        <v>6920284</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9246,57 +9259,61 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
+          <t>Sebastian Kirppu, Karolin Hård</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>110875556</v>
+        <v>110860501</v>
       </c>
       <c r="B83" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Juånäset, Mpd</t>
+          <t>Juånäsberget, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>521145</v>
+        <v>521152</v>
       </c>
       <c r="R83" t="n">
-        <v>6919884</v>
+        <v>6920347</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9345,65 +9362,64 @@
           <t>Barrnaturskog lövrik barrblandskog</t>
         </is>
       </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
-      </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
+          <t>Sebastian Kirppu, Karolin Hård</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>110875579</v>
+        <v>110860502</v>
       </c>
       <c r="B84" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Juånäset, Mpd</t>
+          <t>Juånäsberget, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>520770</v>
+        <v>521102</v>
       </c>
       <c r="R84" t="n">
-        <v>6919888</v>
+        <v>6920392</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9452,65 +9468,64 @@
           <t>Barrnaturskog lövrik barrblandskog</t>
         </is>
       </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
-      </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
+          <t>Sebastian Kirppu, Karolin Hård</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>110875582</v>
+        <v>110875615</v>
       </c>
       <c r="B85" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>520721</v>
+        <v>520792</v>
       </c>
       <c r="R85" t="n">
-        <v>6919849</v>
+        <v>6920150</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9557,11 +9572,6 @@
       <c r="AI85" t="inlineStr">
         <is>
           <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -9579,45 +9589,49 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>110875621</v>
+        <v>110875616</v>
       </c>
       <c r="B86" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>520967</v>
+        <v>520853</v>
       </c>
       <c r="R86" t="n">
-        <v>6920100</v>
+        <v>6920144</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9664,11 +9678,6 @@
       <c r="AI86" t="inlineStr">
         <is>
           <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -9686,45 +9695,49 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>110875625</v>
+        <v>110875622</v>
       </c>
       <c r="B87" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>521045</v>
+        <v>520967</v>
       </c>
       <c r="R87" t="n">
-        <v>6920117</v>
+        <v>6920100</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9771,11 +9784,6 @@
       <c r="AI87" t="inlineStr">
         <is>
           <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -9793,32 +9801,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>110875569</v>
+        <v>110875627</v>
       </c>
       <c r="B88" t="n">
-        <v>80392</v>
+        <v>99118</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9828,10 +9836,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>520937</v>
+        <v>521039</v>
       </c>
       <c r="R88" t="n">
-        <v>6919918</v>
+        <v>6920135</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9895,45 +9903,49 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>110875629</v>
+        <v>110875628</v>
       </c>
       <c r="B89" t="n">
-        <v>80432</v>
+        <v>99118</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>521153</v>
+        <v>521023</v>
       </c>
       <c r="R89" t="n">
-        <v>6920292</v>
+        <v>6920151</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9997,52 +10009,52 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119009759</v>
+        <v>110875630</v>
       </c>
       <c r="B90" t="n">
-        <v>58114</v>
+        <v>99118</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Juånäset, Mpd</t>
+          <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>521139</v>
+        <v>521123</v>
       </c>
       <c r="R90" t="n">
-        <v>6920367</v>
+        <v>6920333</v>
       </c>
       <c r="S90" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10066,27 +10078,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>10:20</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>övr läten</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10101,57 +10098,57 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>110860499</v>
+        <v>110875572</v>
       </c>
       <c r="B91" t="n">
-        <v>99118</v>
+        <v>106244</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Juånäsberget, Mpd</t>
+          <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>521113</v>
+        <v>520920</v>
       </c>
       <c r="R91" t="n">
-        <v>6920246</v>
+        <v>6919915</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10203,61 +10200,61 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>110860500</v>
+        <v>110875575</v>
       </c>
       <c r="B92" t="n">
-        <v>99118</v>
+        <v>106244</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Juånäsberget, Mpd</t>
+          <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>521142</v>
+        <v>520911</v>
       </c>
       <c r="R92" t="n">
-        <v>6920284</v>
+        <v>6919914</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10309,61 +10306,57 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>110860501</v>
+        <v>110875621</v>
       </c>
       <c r="B93" t="n">
-        <v>99118</v>
+        <v>79085</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Juånäsberget, Mpd</t>
+          <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>521152</v>
+        <v>520967</v>
       </c>
       <c r="R93" t="n">
-        <v>6920347</v>
+        <v>6920100</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10412,64 +10405,65 @@
           <t>Barrnaturskog lövrik barrblandskog</t>
         </is>
       </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>110860502</v>
+        <v>110875625</v>
       </c>
       <c r="B94" t="n">
-        <v>99118</v>
+        <v>79085</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Juånäsberget, Mpd</t>
+          <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>521102</v>
+        <v>521045</v>
       </c>
       <c r="R94" t="n">
-        <v>6920392</v>
+        <v>6920117</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10518,64 +10512,65 @@
           <t>Barrnaturskog lövrik barrblandskog</t>
         </is>
       </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>110875630</v>
+        <v>110875569</v>
       </c>
       <c r="B95" t="n">
-        <v>99118</v>
+        <v>80392</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Holmnäset, Mpd</t>
+          <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>521123</v>
+        <v>520937</v>
       </c>
       <c r="R95" t="n">
-        <v>6920333</v>
+        <v>6919918</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10602,12 +10597,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10618,6 +10613,11 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Barrnaturskog lövrik barrblandskog</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -10634,10 +10634,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119009723</v>
+        <v>119010385</v>
       </c>
       <c r="B96" t="n">
-        <v>58649</v>
+        <v>57950</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10645,16 +10645,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103057</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10667,19 +10667,27 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>521428</v>
+        <v>521530</v>
       </c>
       <c r="R96" t="n">
-        <v>6919694</v>
+        <v>6919870</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10703,22 +10711,27 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>trumning</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10745,48 +10758,52 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>110875541</v>
+        <v>119009726</v>
       </c>
       <c r="B97" t="n">
-        <v>97358</v>
+        <v>57132</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>53</v>
+        <v>102612</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>521353</v>
+        <v>521444</v>
       </c>
       <c r="R97" t="n">
-        <v>6920115</v>
+        <v>6919802</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10810,12 +10827,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>05:10</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>05:10</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10826,66 +10853,65 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>110876026</v>
+        <v>119009723</v>
       </c>
       <c r="B98" t="n">
-        <v>80432</v>
+        <v>58649</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>103057</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>521353</v>
+        <v>521428</v>
       </c>
       <c r="R98" t="n">
-        <v>6920115</v>
+        <v>6919694</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -10912,12 +10938,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10928,67 +10964,54 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119009731</v>
+        <v>119009727</v>
       </c>
       <c r="B99" t="n">
-        <v>57950</v>
+        <v>99118</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -10996,13 +11019,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>521477</v>
+        <v>521451</v>
       </c>
       <c r="R99" t="n">
-        <v>6920023</v>
+        <v>6919823</v>
       </c>
       <c r="S99" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11044,17 +11067,13 @@
           <t>05:10</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>övr läte</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11073,60 +11092,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119010385</v>
+        <v>110875541</v>
       </c>
       <c r="B100" t="n">
-        <v>57950</v>
+        <v>97358</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>521530</v>
+        <v>521353</v>
       </c>
       <c r="R100" t="n">
-        <v>6919870</v>
+        <v>6920115</v>
       </c>
       <c r="S100" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11150,27 +11157,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>04:00</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>trumning</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11181,68 +11173,69 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>Barrnaturskog lövrik barrblandskog</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119009726</v>
+        <v>110876026</v>
       </c>
       <c r="B101" t="n">
-        <v>57132</v>
+        <v>80432</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>521444</v>
+        <v>521353</v>
       </c>
       <c r="R101" t="n">
-        <v>6919802</v>
+        <v>6920115</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11266,22 +11259,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>05:10</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>05:10</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11292,48 +11275,53 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>Barrnaturskog lövrik barrblandskog</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119009647</v>
+        <v>119009731</v>
       </c>
       <c r="B102" t="n">
-        <v>58114</v>
+        <v>57950</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -11341,19 +11329,27 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>521377</v>
+        <v>521477</v>
       </c>
       <c r="R102" t="n">
-        <v>6919935</v>
+        <v>6920023</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11377,22 +11373,27 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>05:10</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>05:10</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>övr läte</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11419,37 +11420,37 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>110875537</v>
+        <v>119009647</v>
       </c>
       <c r="B103" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11458,10 +11459,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>521353</v>
+        <v>521377</v>
       </c>
       <c r="R103" t="n">
-        <v>6920115</v>
+        <v>6919935</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11488,12 +11489,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11504,28 +11515,23 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>Barrnaturskog lövrik barrblandskog</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>110875540</v>
+        <v>110875537</v>
       </c>
       <c r="B104" t="n">
         <v>99118</v>
@@ -11564,10 +11570,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>521354</v>
+        <v>521353</v>
       </c>
       <c r="R104" t="n">
-        <v>6920153</v>
+        <v>6920115</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11631,7 +11637,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>110875542</v>
+        <v>110875540</v>
       </c>
       <c r="B105" t="n">
         <v>99118</v>
@@ -11661,7 +11667,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -11670,10 +11676,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>521378</v>
+        <v>521354</v>
       </c>
       <c r="R105" t="n">
-        <v>6920045</v>
+        <v>6920153</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11737,7 +11743,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>110875543</v>
+        <v>110875542</v>
       </c>
       <c r="B106" t="n">
         <v>99118</v>
@@ -11776,10 +11782,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>521383</v>
+        <v>521378</v>
       </c>
       <c r="R106" t="n">
-        <v>6920027</v>
+        <v>6920045</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11843,7 +11849,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>110875546</v>
+        <v>110875543</v>
       </c>
       <c r="B107" t="n">
         <v>99118</v>
@@ -11873,7 +11879,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -11885,7 +11891,7 @@
         <v>521383</v>
       </c>
       <c r="R107" t="n">
-        <v>6919949</v>
+        <v>6920027</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11949,7 +11955,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119009727</v>
+        <v>110875546</v>
       </c>
       <c r="B108" t="n">
         <v>99118</v>
@@ -11977,24 +11983,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Juånäset, Mpd</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>521451</v>
+        <v>521383</v>
       </c>
       <c r="R108" t="n">
-        <v>6919823</v>
+        <v>6919949</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12018,22 +12024,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>05:10</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>05:10</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12042,19 +12038,23 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>Barrnaturskog lövrik barrblandskog</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
